--- a/nonlinear_least_squares_rmse.xlsx
+++ b/nonlinear_least_squares_rmse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kioskUser0\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aglan001\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D39E84-E912-42D1-89D8-EE61B6C696FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AD2CB7-4714-448A-852B-D5B128A8B3B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>SNR</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>window size 1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -112,10 +109,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -327,7 +320,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -335,8 +328,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,7 +507,9 @@
       <c r="I9" s="1">
         <v>6</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1">
+        <v>1.0132078965526199</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -590,8 +585,8 @@
       <c r="I12" s="1">
         <v>6</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>6</v>
+      <c r="J12" s="2">
+        <v>4.9601277077255297</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
@@ -668,7 +663,9 @@
       <c r="I15" s="1">
         <v>6</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1">
+        <v>4.9524156416501999E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -692,7 +689,9 @@
       <c r="I16" s="1">
         <v>4</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1">
+        <v>0.49417421197821798</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
@@ -742,9 +741,11 @@
       <c r="I18" s="1">
         <v>6</v>
       </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J18" s="1">
+        <v>9.5958478672901998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>40</v>
       </c>
@@ -766,9 +767,11 @@
       <c r="I19" s="1">
         <v>4</v>
       </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J19" s="1">
+        <v>1.1279734228781899</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>40</v>
       </c>
@@ -790,7 +793,9 @@
       <c r="I20" s="1">
         <v>5</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1">
+        <v>2.8257090729404402</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -814,7 +819,9 @@
       <c r="I21" s="1">
         <v>6</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1">
+        <v>0.83198877099346302</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
@@ -890,9 +897,11 @@
       <c r="I24" s="1">
         <v>6</v>
       </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J24" s="1">
+        <v>3.7585206362481498E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>80</v>
       </c>
@@ -914,9 +923,11 @@
       <c r="I25" s="1">
         <v>4</v>
       </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J25" s="1">
+        <v>3.1616222519402501E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>80</v>
       </c>
@@ -938,7 +949,9 @@
       <c r="I26" s="1">
         <v>5</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="1">
+        <v>6.8502052246504101E-4</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
@@ -962,7 +975,9 @@
       <c r="I27" s="1">
         <v>6</v>
       </c>
-      <c r="J27" s="1"/>
+      <c r="J27" s="1">
+        <v>9.3339787616666297E-4</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -1038,11 +1053,12 @@
       <c r="I30" s="1">
         <v>6</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>6</v>
+      <c r="J30" s="2">
+        <v>1.85671775667838E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>